--- a/examples/Lecanemab/CEREBRO_X_Completed_Data_Lecanemab.xlsx
+++ b/examples/Lecanemab/CEREBRO_X_Completed_Data_Lecanemab.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-05T08:04:52Z  | Pipeline: v20  | Source: CEREBRO_Input_Lecanemab.xlsx</t>
+          <t>Generated: 2026-09-05T18:05:11Z  | Pipeline: v20  | Source: CEREBRO_Input_Lecanemab.xlsx</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>62.73</v>
+        <v>62.14</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>62.38</v>
+        <v>61.79</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.01</v>
+        <v>53.65</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>23.01</v>
+        <v>26.14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0115</v>
+        <v>0.0131</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>Brain AUC = 4.12 units·h, plasma AUC = 358.06 units·h, ratio = 0.0115. Cmax_brain = 0.21 at t = 8.0h. BELOW THRESHOLD AUC ratio.</t>
+          <t>Brain AUC = 0.81 units·h, plasma AUC = 61.60 units·h, ratio = 0.0131. Cmax_brain = 0.06 at t = 1.9h. BELOW THRESHOLD AUC ratio.</t>
         </is>
       </c>
     </row>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>23.01</v>
+        <v>26.14</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0115</v>
+        <v>0.0131</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>Brain AUC = 4.12 units·h, plasma AUC = 358.06 units·h, ratio = 0.0115. Cmax_brain = 0.21 at t = 8.0h. BELOW THRESHOLD AUC ratio.</t>
+          <t>Brain AUC = 0.81 units·h, plasma AUC = 61.60 units·h, ratio = 0.0131. Cmax_brain = 0.06 at t = 1.9h. BELOW THRESHOLD AUC ratio.</t>
         </is>
       </c>
     </row>
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>7.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0038</v>
+        <v>0.0044</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>Brain AUC = 1.37 units·h, plasma AUC = 358.44 units·h, ratio = 0.0038. Cmax_brain = 0.07 at t = 8.0h. BELOW THRESHOLD AUC ratio.</t>
+          <t>Brain AUC = 0.27 units·h, plasma AUC = 61.61 units·h, ratio = 0.0044. Cmax_brain = 0.02 at t = 1.9h. BELOW THRESHOLD AUC ratio.</t>
         </is>
       </c>
     </row>
@@ -9458,8 +9458,14 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>&gt;Lecanemab_VH
-QVQLVQSGAEVKKPGSSVKVSCKASGYTFTNYGMNWVRQAPGQGLEWMGWINTYTGEPTYTDDFKGRVTITTDTSTSTAYMELSSLRSEDTAVYYCARGGYDGRGFDYWGQGTLVTVSS</t>
+          <t>&gt;Lecanemab_Heavy_Chain_1
+EVQLVESGGGLVQPGGSLRLSCSASGFTFSSFGMHWVRQAPGKGLEWVAYISSGSSTIYYGDTVKGRFTISRDNAKNSLFLQMSSLRAEDTAVYYCAREGGYYYGRSYYTMDYWGQGTTVTVSSASTKGPSVFPLAPSSKSTSGGTAALGCLVKDYFPEPVTVSWNSGALTSGVHTFPAVLQSSGLYSLSSVVTVPSSSLGTQTYICNVNHKPSNTKVDKKVEPKSCDKTHTCPPCPAPELLGGPSVFLFPPKPKDTLMISRTPEVTCVVVDVSHEDPEVKFNWYVDGVEVHNAKTKPREEQYNSTYRVVSVLTVLHQDWLNGKEYKCKVSNKALPAPIEKTISKAKGQPREPQVYTLPPSRDELTKNQVSLTCLVKGFYPSDIAVEWESNGQPENNYKTTPPVLDSDGSFFLYSKLTVDKSRWQQGNVFSCSVMHEALHNHYTQKSLSLSPGK
+&gt;Lecanemab_Heavy_Chain_2
+EVQLVESGGGLVQPGGSLRLSCSASGFTFSSFGMHWVRQAPGKGLEWVAYISSGSSTIYYGDTVKGRFTISRDNAKNSLFLQMSSLRAEDTAVYYCAREGGYYYGRSYYTMDYWGQGTTVTVSSASTKGPSVFPLAPSSKSTSGGTAALGCLVKDYFPEPVTVSWNSGALTSGVHTFPAVLQSSGLYSLSSVVTVPSSSLGTQTYICNVNHKPSNTKVDKKVEPKSCDKTHTCPPCPAPELLGGPSVFLFPPKPKDTLMISRTPEVTCVVVDVSHEDPEVKFNWYVDGVEVHNAKTKPREEQYNSTYRVVSVLTVLHQDWLNGKEYKCKVSNKALPAPIEKTISKAKGQPREPQVYTLPPSRDELTKNQVSLTCLVKGFYPSDIAVEWESNGQPENNYKTTPPVLDSDGSFFLYSKLTVDKSRWQQGNVFSCSVMHEALHNHYTQKSLSLSPGK
+&gt;Lecanemab_Light_Chain_1
+DVVMTQSPLSLPVTPGAPASISCRSSQSIVHSNGNTYLEWYLQKPGQSPKLLIYKVSNRFSGVPDRFSGSGSGTDFTLRISRVEAEDVGIYYCFQGSHVPPTFGPGTKLEIKRTVAAPSVFIFPPSDEQLKSGTASVVCLLNNFYPREAKVQWKVDNALQSGNSQESVTEQDSKDSTYSLSSTLTLSKADYEKHKVYACEVTHQGLSSPVTKSFNRGEC
+&gt;Lecanemab_Light_Chain_2
+DVVMTQSPLSLPVTPGAPASISCRSSQSIVHSNGNTYLEWYLQKPGQSPKLLIYKVSNRFSGVPDRFSGSGSGTDFTLRISRVEAEDVGIYYCFQGSHVPPTFGPGTKLEIKRTVAAPSVFIFPPSDEQLKSGTASVVCLLNNFYPREAKVQWKVDNALQSGNSQESVTEQDSKDSTYSLSSTLTLSKADYEKHKVYACEVTHQGLSSPVTKSFNRGEC</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr"/>
@@ -9687,7 +9693,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
@@ -9720,7 +9726,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="C17" s="13" t="inlineStr"/>
       <c r="D17" s="14" t="inlineStr">
@@ -9749,7 +9755,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>5.27</v>
+        <v>8.48</v>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
@@ -9887,7 +9893,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>77.0123</v>
+        <v>5.2769</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
@@ -9920,7 +9926,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>-0.113</v>
+        <v>-1.278</v>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
       <c r="D23" s="14" t="inlineStr">
@@ -10544,11 +10550,11 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -10652,11 +10658,11 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>20.46</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>-683.17</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -10796,11 +10802,11 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -12387,11 +12393,11 @@
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>23.01</v>
+        <v>26.14</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.0115</t>
+          <t>0.0131</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -13833,10 +13839,10 @@
         </is>
       </c>
       <c r="U4" s="28" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V4" s="28" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W4" s="28" t="n">
         <v>0</v>
@@ -13892,7 +13898,7 @@
         <v>1</v>
       </c>
       <c r="AN4" s="28" t="n">
-        <v>62.73</v>
+        <v>62.14</v>
       </c>
       <c r="AO4" s="28" t="n">
         <v>58.28</v>
@@ -13904,7 +13910,7 @@
         <v>60.68</v>
       </c>
       <c r="AR4" s="28" t="n">
-        <v>73.8</v>
+        <v>71</v>
       </c>
       <c r="AS4" s="28" t="n">
         <v>65</v>
@@ -13927,7 +13933,7 @@
         </is>
       </c>
       <c r="AY4" s="28" t="n">
-        <v>57.03</v>
+        <v>56.49</v>
       </c>
       <c r="AZ4" s="28" t="inlineStr">
         <is>
@@ -14074,10 +14080,10 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -14133,7 +14139,7 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>62.38</v>
+        <v>61.79</v>
       </c>
       <c r="AO5" t="n">
         <v>57.83</v>
@@ -14145,7 +14151,7 @@
         <v>60.68</v>
       </c>
       <c r="AR5" t="n">
-        <v>73.79000000000001</v>
+        <v>71</v>
       </c>
       <c r="AS5" t="n">
         <v>65</v>
@@ -14168,7 +14174,7 @@
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>56.71</v>
+        <v>56.18</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -14315,10 +14321,10 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -14374,19 +14380,19 @@
         <v>3</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.01</v>
+        <v>53.65</v>
       </c>
       <c r="AO6" t="n">
         <v>36.09</v>
       </c>
       <c r="AP6" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="AQ6" t="n">
         <v>64.29000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>71.95999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="AS6" t="n">
         <v>39.13</v>
@@ -14409,7 +14415,7 @@
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>45.77</v>
+        <v>45.46</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -14556,10 +14562,10 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -14615,19 +14621,19 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.74</v>
+        <v>53.25</v>
       </c>
       <c r="AO7" t="n">
         <v>56.84</v>
       </c>
       <c r="AP7" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="AQ7" t="n">
         <v>64.29000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>73.11</v>
+        <v>70.38</v>
       </c>
       <c r="AS7" t="n">
         <v>60</v>
@@ -14650,7 +14656,7 @@
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>56.57</v>
+        <v>56.05</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -14797,10 +14803,10 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -14856,7 +14862,7 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.67</v>
+        <v>46.26</v>
       </c>
       <c r="AO8" t="n">
         <v>57.61</v>
@@ -14868,7 +14874,7 @@
         <v>78.76000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>73.68000000000001</v>
+        <v>71</v>
       </c>
       <c r="AS8" t="n">
         <v>56.67</v>
@@ -14891,7 +14897,7 @@
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>58.33</v>
+        <v>57.82</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -15038,10 +15044,10 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -15097,19 +15103,19 @@
         <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>45.01</v>
+        <v>44.62</v>
       </c>
       <c r="AO9" t="n">
         <v>59.08</v>
       </c>
       <c r="AP9" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="AQ9" t="n">
         <v>59.78</v>
       </c>
       <c r="AR9" t="n">
-        <v>71.68000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="AS9" t="n">
         <v>55</v>
@@ -15132,7 +15138,7 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>56.27</v>
+        <v>55.77</v>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
@@ -15279,10 +15285,10 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -15338,7 +15344,7 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.25</v>
+        <v>43.83</v>
       </c>
       <c r="AO10" t="n">
         <v>57.17</v>
@@ -15350,7 +15356,7 @@
         <v>81.72</v>
       </c>
       <c r="AR10" t="n">
-        <v>74.59</v>
+        <v>71.62</v>
       </c>
       <c r="AS10" t="n">
         <v>61.67</v>
@@ -15373,7 +15379,7 @@
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>59.01</v>
+        <v>58.44</v>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
@@ -15520,10 +15526,10 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>13060.26</v>
+        <v>147091.66</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.147</v>
+        <v>-0.114</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -15579,7 +15585,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.14</v>
+        <v>38.71</v>
       </c>
       <c r="AO11" t="n">
         <v>41.77</v>
@@ -15591,7 +15597,7 @@
         <v>81.72</v>
       </c>
       <c r="AR11" t="n">
-        <v>74.64</v>
+        <v>71.62</v>
       </c>
       <c r="AS11" t="n">
         <v>60.6</v>
@@ -15614,7 +15620,7 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>52.19</v>
+        <v>51.61</v>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
@@ -16127,7 +16133,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>62.73</v>
+        <v>62.14</v>
       </c>
       <c r="D5" s="31" t="n">
         <v>58.28</v>
@@ -16139,7 +16145,7 @@
         <v>60.68</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>73.8</v>
+        <v>71</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>65</v>
@@ -16190,7 +16196,7 @@
         <v>3.38</v>
       </c>
       <c r="X5" s="35" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="31" t="n">
         <v>46.25</v>
@@ -16198,8 +16204,8 @@
       <c r="Z5" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="AA5" s="32" t="n">
-        <v>20.46</v>
+      <c r="AA5" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="AB5" s="33" t="n">
         <v>75.95</v>
@@ -16211,7 +16217,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="34" t="n">
         <v>80</v>
@@ -16332,7 +16338,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>62.38</v>
+        <v>61.79</v>
       </c>
       <c r="D6" s="31" t="n">
         <v>57.83</v>
@@ -16344,7 +16350,7 @@
         <v>60.68</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>73.79000000000001</v>
+        <v>71</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>65</v>
@@ -16395,7 +16401,7 @@
         <v>3.38</v>
       </c>
       <c r="X6" s="35" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="31" t="n">
         <v>46.25</v>
@@ -16403,8 +16409,8 @@
       <c r="Z6" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="AA6" s="32" t="n">
-        <v>20.46</v>
+      <c r="AA6" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="AB6" s="33" t="n">
         <v>61.42</v>
@@ -16416,7 +16422,7 @@
         <v>0</v>
       </c>
       <c r="AE6" s="35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="34" t="n">
         <v>80</v>
@@ -16537,19 +16543,19 @@
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>54.01</v>
+        <v>53.65</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>36.09</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="F7" s="33" t="n">
         <v>64.29000000000001</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>71.95999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="H7" s="32" t="n">
         <v>39.13</v>
@@ -16600,7 +16606,7 @@
         <v>0.9</v>
       </c>
       <c r="X7" s="35" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="31" t="n">
         <v>46.25</v>
@@ -16609,7 +16615,7 @@
         <v>20</v>
       </c>
       <c r="AA7" s="35" t="n">
-        <v>9.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="35" t="n">
         <v>19.5</v>
@@ -16621,7 +16627,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="35" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="34" t="n">
         <v>80</v>
@@ -16742,19 +16748,19 @@
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>53.74</v>
+        <v>53.25</v>
       </c>
       <c r="D8" s="31" t="n">
         <v>56.84</v>
       </c>
       <c r="E8" s="31" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="F8" s="33" t="n">
         <v>64.29000000000001</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>73.11</v>
+        <v>70.38</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>60</v>
@@ -16805,7 +16811,7 @@
         <v>3.38</v>
       </c>
       <c r="X8" s="35" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="31" t="n">
         <v>46.25</v>
@@ -16814,7 +16820,7 @@
         <v>20</v>
       </c>
       <c r="AA8" s="35" t="n">
-        <v>19.21</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="34" t="n">
         <v>85.36</v>
@@ -16826,7 +16832,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="34" t="n">
         <v>80</v>
@@ -16947,7 +16953,7 @@
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>46.67</v>
+        <v>46.26</v>
       </c>
       <c r="D9" s="31" t="n">
         <v>57.61</v>
@@ -16959,7 +16965,7 @@
         <v>78.76000000000001</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>73.68000000000001</v>
+        <v>71</v>
       </c>
       <c r="H9" s="31" t="n">
         <v>56.67</v>
@@ -17010,7 +17016,7 @@
         <v>3.38</v>
       </c>
       <c r="X9" s="35" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="33" t="n">
         <v>77.08</v>
@@ -17019,7 +17025,7 @@
         <v>20</v>
       </c>
       <c r="AA9" s="35" t="n">
-        <v>19.21</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="33" t="n">
         <v>75.95</v>
@@ -17031,7 +17037,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="35" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="34" t="n">
         <v>80</v>
@@ -17152,19 +17158,19 @@
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>45.01</v>
+        <v>44.62</v>
       </c>
       <c r="D10" s="31" t="n">
         <v>59.08</v>
       </c>
       <c r="E10" s="31" t="n">
-        <v>43.79</v>
+        <v>43.75</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>59.78</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>71.68000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="H10" s="31" t="n">
         <v>55</v>
@@ -17215,7 +17221,7 @@
         <v>3.38</v>
       </c>
       <c r="X10" s="35" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="33" t="n">
         <v>61.67</v>
@@ -17224,7 +17230,7 @@
         <v>20</v>
       </c>
       <c r="AA10" s="35" t="n">
-        <v>17.96</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="33" t="n">
         <v>78</v>
@@ -17236,7 +17242,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="34" t="n">
         <v>80</v>
@@ -17357,7 +17363,7 @@
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>44.25</v>
+        <v>43.83</v>
       </c>
       <c r="D11" s="31" t="n">
         <v>57.17</v>
@@ -17369,7 +17375,7 @@
         <v>81.72</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>74.59</v>
+        <v>71.62</v>
       </c>
       <c r="H11" s="33" t="n">
         <v>61.67</v>
@@ -17428,8 +17434,8 @@
       <c r="Z11" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="AA11" s="32" t="n">
-        <v>21.71</v>
+      <c r="AA11" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="AB11" s="33" t="n">
         <v>61.42</v>
@@ -17441,7 +17447,7 @@
         <v>0</v>
       </c>
       <c r="AE11" s="35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="34" t="n">
         <v>80</v>
@@ -17562,7 +17568,7 @@
         </is>
       </c>
       <c r="C12" s="37" t="n">
-        <v>39.14</v>
+        <v>38.71</v>
       </c>
       <c r="D12" s="31" t="n">
         <v>41.77</v>
@@ -17574,7 +17580,7 @@
         <v>81.72</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>74.64</v>
+        <v>71.62</v>
       </c>
       <c r="H12" s="33" t="n">
         <v>60.6</v>
@@ -17633,8 +17639,8 @@
       <c r="Z12" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="AA12" s="32" t="n">
-        <v>21.71</v>
+      <c r="AA12" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="AB12" s="35" t="n">
         <v>19.5</v>
@@ -17646,7 +17652,7 @@
         <v>0</v>
       </c>
       <c r="AE12" s="35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="34" t="n">
         <v>80</v>
@@ -17809,7 +17815,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>62.7 / 100</t>
+          <t>62.1 / 100</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
@@ -17826,7 +17832,7 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>Tf-PEG-Liposome: composite CNS-principle score = 62.7/100 (ACCEPTABLE). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (73.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Tf-PEG-Liposome: composite CNS-principle score = 62.1/100 (ACCEPTABLE). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (71.0/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17838,7 +17844,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 35/100  G3_Stability: 61/100  G4_Safety: 74/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 56/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 35/100  G3_Stability: 61/100  G4_Safety: 71/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 56/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17894,51 +17900,51 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.4/100</t>
+          <t>2.0/100</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17961,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>62.4 / 100</t>
+          <t>61.8 / 100</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
@@ -17972,7 +17978,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>RVG29-Liposome-pH: composite CNS-principle score = 62.4/100 (ACCEPTABLE). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (73.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>RVG29-Liposome-pH: composite CNS-principle score = 61.8/100 (ACCEPTABLE). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (71.0/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17990,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 35/100  G3_Stability: 61/100  G4_Safety: 74/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 54/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 35/100  G3_Stability: 61/100  G4_Safety: 71/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 54/100  G7_DrugDDS_Fit: 68/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18040,51 +18046,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.4/100</t>
+          <t>2.0/100</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.9/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18107,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>54.0 / 100</t>
+          <t>53.6 / 100</t>
         </is>
       </c>
       <c r="D24" s="36" t="inlineStr">
@@ -18118,7 +18124,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>AAV9-vector: composite CNS-principle score = 54.0/100 (ACCEPTABLE). Carrier: aav9, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G4 Safety (72.0/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>AAV9-vector: composite CNS-principle score = 53.6/100 (ACCEPTABLE). Carrier: aav9, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G4 Safety (70.4/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18130,7 +18136,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 36/100  G2_Release_Kinetics: 44/100  G3_Stability: 64/100  G4_Safety: 72/100  G5_Glymphatic_BBB: 39/100  G6_Manufacturability: 47/100  G7_DrugDDS_Fit: 64/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 36/100  G2_Release_Kinetics: 44/100  G3_Stability: 64/100  G4_Safety: 70/100  G5_Glymphatic_BBB: 39/100  G6_Manufacturability: 47/100  G7_DrugDDS_Fit: 64/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18186,51 +18192,51 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.9/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.5/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.2/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Score = 100 - 3·($/mg estimate, drug+carrier+ligand+API). Drug</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18253,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>53.7 / 100</t>
+          <t>53.2 / 100</t>
         </is>
       </c>
       <c r="D34" s="36" t="inlineStr">
@@ -18264,7 +18270,7 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>ApoE-LNP: composite CNS-principle score = 53.7/100 (ACCEPTABLE). Carrier: lnp, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (73.1/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>ApoE-LNP: composite CNS-principle score = 53.2/100 (ACCEPTABLE). Carrier: lnp, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (70.4/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18282,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 57/100  G2_Release_Kinetics: 44/100  G3_Stability: 64/100  G4_Safety: 73/100  G5_Glymphatic_BBB: 60/100  G6_Manufacturability: 49/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 57/100  G2_Release_Kinetics: 44/100  G3_Stability: 64/100  G4_Safety: 70/100  G5_Glymphatic_BBB: 60/100  G6_Manufacturability: 49/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18332,51 +18338,51 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2.6/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Score = 100 - 3·($/mg estimate, drug+carrier+ligand+API). Drug</t>
         </is>
       </c>
     </row>
@@ -18393,7 +18399,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>46.7 / 100</t>
+          <t>46.3 / 100</t>
         </is>
       </c>
       <c r="D44" s="37" t="inlineStr">
@@ -18410,7 +18416,7 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Tf-SLN-Stealth: composite CNS-principle score = 46.7/100 (MARGINAL). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G3 Stability (78.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Tf-SLN-Stealth: composite CNS-principle score = 46.3/100 (MARGINAL). Carrier: solid_lipid, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G3 Stability (78.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18428,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 34/100  G3_Stability: 79/100  G4_Safety: 74/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 61/100  G7_DrugDDS_Fit: 69/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 58/100  G2_Release_Kinetics: 34/100  G3_Stability: 79/100  G4_Safety: 71/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 61/100  G7_DrugDDS_Fit: 69/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18478,51 +18484,51 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.4/100</t>
+          <t>2.0/100</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2.2/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D51" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18545,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>45.0 / 100</t>
+          <t>44.6 / 100</t>
         </is>
       </c>
       <c r="D54" s="37" t="inlineStr">
@@ -18556,7 +18562,7 @@
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Lf-Polymer-Micelle: composite CNS-principle score = 45.0/100 (MARGINAL). Carrier: micelle, size 0.0 nm, ζ +0.0 mV, ligand: Lactoferrin. Strongest group: G4 Safety (71.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Lf-Polymer-Micelle: composite CNS-principle score = 44.6/100 (MARGINAL). Carrier: micelle, size 0.0 nm, ζ +0.0 mV, ligand: Lactoferrin. Strongest group: G4 Safety (69.1/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18574,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 59/100  G2_Release_Kinetics: 44/100  G3_Stability: 60/100  G4_Safety: 72/100  G5_Glymphatic_BBB: 55/100  G6_Manufacturability: 56/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 59/100  G2_Release_Kinetics: 44/100  G3_Stability: 60/100  G4_Safety: 69/100  G5_Glymphatic_BBB: 55/100  G6_Manufacturability: 56/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18624,51 +18630,51 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.4/100</t>
+          <t>2.0/100</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2.5/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18691,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>44.2 / 100</t>
+          <t>43.8 / 100</t>
         </is>
       </c>
       <c r="D64" s="37" t="inlineStr">
@@ -18702,7 +18708,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>RVG29-PLGA-NP: composite CNS-principle score = 44.3/100 (MARGINAL). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G3 Stability (81.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>RVG29-PLGA-NP: composite CNS-principle score = 43.8/100 (MARGINAL). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G3 Stability (81.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18720,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 57/100  G2_Release_Kinetics: 44/100  G3_Stability: 82/100  G4_Safety: 75/100  G5_Glymphatic_BBB: 62/100  G6_Manufacturability: 61/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 57/100  G2_Release_Kinetics: 44/100  G3_Stability: 82/100  G4_Safety: 72/100  G5_Glymphatic_BBB: 62/100  G6_Manufacturability: 61/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18770,41 +18776,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.0/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: 100 × exp(-corona_thickness/10); thickness from carrier (|zeta</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18814,7 +18820,7 @@
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Score = 100 - 3·($/mg estimate, drug+carrier+ligand+API). Drug</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18837,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>39.1 / 100</t>
+          <t>38.7 / 100</t>
         </is>
       </c>
       <c r="D74" s="37" t="inlineStr">
@@ -18848,7 +18854,7 @@
       </c>
       <c r="B75" s="22" t="inlineStr">
         <is>
-          <t>Bare-PLGA: composite CNS-principle score = 39.1/100 (MARGINAL). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G3 Stability (81.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Bare-PLGA: composite CNS-principle score = 38.7/100 (MARGINAL). Carrier: plga, size 0.0 nm, ζ +0.0 mV, ligand: None. Strongest group: G3 Stability (81.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18866,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 42/100  G2_Release_Kinetics: 44/100  G3_Stability: 82/100  G4_Safety: 75/100  G5_Glymphatic_BBB: 61/100  G6_Manufacturability: 59/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 42/100  G2_Release_Kinetics: 44/100  G3_Stability: 82/100  G4_Safety: 72/100  G5_Glymphatic_BBB: 61/100  G6_Manufacturability: 59/100  G7_DrugDDS_Fit: 66/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -18916,41 +18922,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.9/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: AUC_brain/AUC_plasma proxy; 3-compartment surrogate</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.8/100</t>
+          <t>0.0/100</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: brain% = BBB · ligand · size_match · 100; 100 if ≥5%</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Mean of (hemolysis penalized by drug net+ charge, complement p</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18960,7 +18966,7 @@
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: t50 from carrier kinetics × drug-membrane partition factor (10</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Score = 100 - 3·($/mg estimate, drug+carrier+ligand+API). Drug</t>
         </is>
       </c>
     </row>
@@ -19671,11 +19677,11 @@
         </is>
       </c>
       <c r="E18" s="43" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -19793,12 +19799,12 @@
           <t>Nanotoxicity &amp; Immunogenicity Screening</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>20.46</v>
+      <c r="E21" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>-683.17</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -19958,11 +19964,11 @@
         </is>
       </c>
       <c r="E25" s="43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -22008,11 +22014,11 @@
         </is>
       </c>
       <c r="E75" s="43" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -22130,12 +22136,12 @@
           <t>Nanotoxicity &amp; Immunogenicity Screening</t>
         </is>
       </c>
-      <c r="E78" s="9" t="n">
-        <v>20.46</v>
+      <c r="E78" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>-683.17</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -22295,11 +22301,11 @@
         </is>
       </c>
       <c r="E82" s="43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -24345,11 +24351,11 @@
         </is>
       </c>
       <c r="E132" s="43" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -24468,11 +24474,11 @@
         </is>
       </c>
       <c r="E135" s="43" t="n">
-        <v>9.83</v>
+        <v>0</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>-693.79</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -24632,11 +24638,11 @@
         </is>
       </c>
       <c r="E139" s="43" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -26682,11 +26688,11 @@
         </is>
       </c>
       <c r="E189" s="43" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -26805,11 +26811,11 @@
         </is>
       </c>
       <c r="E192" s="43" t="n">
-        <v>19.21</v>
+        <v>0</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>-684.42</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -26969,11 +26975,11 @@
         </is>
       </c>
       <c r="E196" s="43" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -29019,11 +29025,11 @@
         </is>
       </c>
       <c r="E246" s="43" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -29142,11 +29148,11 @@
         </is>
       </c>
       <c r="E249" s="43" t="n">
-        <v>19.21</v>
+        <v>0</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>-684.42</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -29306,11 +29312,11 @@
         </is>
       </c>
       <c r="E253" s="43" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -31356,11 +31362,11 @@
         </is>
       </c>
       <c r="E303" s="43" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -31479,11 +31485,11 @@
         </is>
       </c>
       <c r="E306" s="43" t="n">
-        <v>17.96</v>
+        <v>0</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>-685.67</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -31643,11 +31649,11 @@
         </is>
       </c>
       <c r="E310" s="43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -33815,12 +33821,12 @@
           <t>Nanotoxicity &amp; Immunogenicity Screening</t>
         </is>
       </c>
-      <c r="E363" s="9" t="n">
-        <v>21.71</v>
+      <c r="E363" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>-681.92</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -33980,11 +33986,11 @@
         </is>
       </c>
       <c r="E367" s="43" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr">
@@ -36152,12 +36158,12 @@
           <t>Nanotoxicity &amp; Immunogenicity Screening</t>
         </is>
       </c>
-      <c r="E420" s="9" t="n">
-        <v>21.71</v>
+      <c r="E420" s="43" t="n">
+        <v>0</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>-681.92</t>
         </is>
       </c>
       <c r="G420" s="5" t="inlineStr">
@@ -36317,11 +36323,11 @@
         </is>
       </c>
       <c r="E424" s="43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G424" s="5" t="inlineStr">
@@ -38230,10 +38236,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>23.01</v>
+        <v>26.14</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0115</v>
+        <v>0.0131</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
@@ -38253,7 +38259,7 @@
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>Brain AUC = 4.12 units·h, plasma AUC = 358.06 units·h, ratio = 0.0115. Cmax_brain = 0.21 at t = 8.0h. BELOW THRESHOLD AUC ratio.</t>
+          <t>Brain AUC = 0.81 units·h, plasma AUC = 61.60 units·h, ratio = 0.0131. Cmax_brain = 0.06 at t = 1.9h. BELOW THRESHOLD AUC ratio.</t>
         </is>
       </c>
     </row>
